--- a/new/zh-CN/new.xlsx
+++ b/new/zh-CN/new.xlsx
@@ -115,9 +115,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -145,14 +145,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -180,6 +197,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">

--- a/new/zh-CN/new.xlsx
+++ b/new/zh-CN/new.xlsx
@@ -19,14 +19,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -54,7 +53,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
